--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-12T07:52:32    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-13T08:11:07    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.28s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.38s</t>
+          <t>3.39s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.32s</t>
+          <t>1.33s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.86s</t>
+          <t>0.87s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.46s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.19s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.16</v>
+        <v>21.17</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.78</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.11</v>
+        <v>21.18</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.84</v>
+        <v>21.82</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.86</v>
+        <v>21.87</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.12</v>
+        <v>22.14</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.16</v>
+        <v>21.17</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.78</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.11</v>
+        <v>21.18</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.84</v>
+        <v>21.82</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.86</v>
+        <v>21.87</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.12</v>
+        <v>22.14</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-13T08:11:07    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-14T08:43:35    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.19s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.87s</t>
+          <t>0.88s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.1s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.07</v>
+        <v>10.13</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.17</v>
+        <v>21.13</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.8</v>
+        <v>21.81</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.87</v>
+        <v>21.84</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.18</v>
+        <v>21.19</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.15</v>
+        <v>21.13</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.82</v>
+        <v>21.81</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.87</v>
+        <v>21.92</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.07</v>
+        <v>10.13</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.17</v>
+        <v>21.13</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.8</v>
+        <v>21.81</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.87</v>
+        <v>21.84</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.18</v>
+        <v>21.19</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.15</v>
+        <v>21.13</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.82</v>
+        <v>21.81</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.87</v>
+        <v>21.92</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-14T08:43:35    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-15T08:34:14    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.28s</t>
+          <t>1.27s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.39s</t>
+          <t>3.38s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.32s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.19s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.88s</t>
+          <t>0.87s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.48s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.13</v>
+        <v>10.15</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.13</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.81</v>
+        <v>21.84</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.77</v>
+        <v>21.8</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.84</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.83</v>
+        <v>21.92</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.19</v>
+        <v>21.1</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.13</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.81</v>
+        <v>21.85</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.92</v>
+        <v>21.9</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.14</v>
+        <v>22.15</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.13</v>
+        <v>10.15</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.13</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.81</v>
+        <v>21.84</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.77</v>
+        <v>21.8</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.84</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.83</v>
+        <v>21.92</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.19</v>
+        <v>21.1</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.13</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.81</v>
+        <v>21.85</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.92</v>
+        <v>21.9</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.14</v>
+        <v>22.15</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-15T08:34:14    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-16T08:27:48    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.15</v>
+        <v>10.11</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.09</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.8</v>
+        <v>21.79</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.89</v>
+        <v>21.91</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.92</v>
+        <v>21.91</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.17</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.85</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.9</v>
+        <v>21.88</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.15</v>
+        <v>22.18</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.15</v>
+        <v>10.11</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.09</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.8</v>
+        <v>21.79</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.89</v>
+        <v>21.91</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.92</v>
+        <v>21.91</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.17</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.85</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.9</v>
+        <v>21.88</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.15</v>
+        <v>22.18</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +156,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -200,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +264,15 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,10 +288,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -679,7 +693,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-16T08:27:48    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-17T08:34:53    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -723,22 +737,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.64s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +827,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.29s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -844,7 +858,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.04s</t>
+          <t>1.05s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -875,7 +889,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.38s</t>
+          <t>3.39s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +920,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.32s</t>
+          <t>1.34s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +951,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.19s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -1030,7 +1044,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.2s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1049,19 +1063,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.1s</t>
+          <t>0.85s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1231,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1303,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1339,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1375,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1411,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1447,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.88</v>
+        <v>4.14</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1483,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.91</v>
+        <v>4.07</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1519,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1555,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1627,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1663,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1699,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1735,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1807,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1843,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1879,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1951,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1987,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2023,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2059,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2095,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2131,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2203,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2239,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2275,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2311,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2383,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2455,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2491,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2527,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2563,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2599,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2635,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2671,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2707,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2743,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2779,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.11</v>
+        <v>10.14</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2815,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2851,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.09</v>
+        <v>21.14</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2887,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2923,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.79</v>
+        <v>21.81</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2959,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.91</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2995,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.91</v>
+        <v>21.92</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3031,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3067,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3139,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.17</v>
+        <v>21.15</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3175,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.87</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3211,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.88</v>
+        <v>21.85</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3247,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.18</v>
+        <v>22.11</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3283,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3355,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3391,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3427,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3499,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3535,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3571,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3607,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3643,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3679,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3715,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3751,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3787,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3823,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3859,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3895,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3931,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3967,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +4003,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4039,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4075,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4111,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4147,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4183,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4219,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4255,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4291,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4327,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4363,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4399,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4435,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4471,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4543,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4579,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4615,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4651,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4687,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4723,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4759,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4795,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4831,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4867,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4903,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4939,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4975,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +5011,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5047,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5083,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5119,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5155,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5191,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5227,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5263,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5335,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5371,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5407,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5443,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5479,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5515,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5551,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5587,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5695,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5731,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5767,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5803,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5839,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5875,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5911,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5983,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6019,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6055,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6091,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6127,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6163,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6271,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6307,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6343,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6379,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6415,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6451,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6487,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6559,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6595,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6667,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6703,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6739,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6775,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6811,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6847,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6919,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6991,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7027,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7099,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7243,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7279,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7315,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7387,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7459,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7495,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7531,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7567,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7603,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7711,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7783,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7999,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8107,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8179,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8215,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8251,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8287,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8359,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8395,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8467,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8503,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8539,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8611,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8647,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8683,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8719,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8741,7 +8755,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8791,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8827,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8863,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8899,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9295,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9403,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9511,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9547,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9619,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9655,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9691,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9763,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9907,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9943,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10015,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10087,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10159,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10181,7 +10195,7 @@
         </is>
       </c>
       <c r="G251" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H251" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10267,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10303,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10325,7 +10339,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -10361,7 +10375,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10447,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10483,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10505,7 +10519,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10555,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10591,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10627,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10663,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10699,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10735,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10771,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10807,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10843,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10879,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10915,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10951,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10987,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11023,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11059,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11095,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11131,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11167,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11203,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11239,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11275,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11311,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11347,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11383,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11419,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11455,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11527,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11563,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11635,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11671,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11707,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11743,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11779,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11815,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11851,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11887,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11923,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11959,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11995,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12031,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12067,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12103,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12139,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12175,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12211,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12247,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12283,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12319,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12355,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12391,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12427,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12463,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12499,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12535,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12571,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12607,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12643,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12679,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12715,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12751,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12787,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12823,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12859,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12895,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12931,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12967,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +13003,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13039,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13075,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13111,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13147,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13183,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13219,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13255,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13291,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13327,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13363,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13399,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13435,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13471,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13507,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13543,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13579,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13615,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13651,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13687,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13723,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13759,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13795,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13831,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13867,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13903,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13939,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13975,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +14011,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14047,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14083,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14119,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14155,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14227,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14263,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14299,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14335,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14371,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14407,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14443,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14479,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14515,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14551,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14587,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14623,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14659,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14695,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14731,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14767,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14803,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14839,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14875,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14911,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14947,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14983,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15019,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15055,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15091,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15127,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15163,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15199,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15235,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15271,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15307,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15343,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15379,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15415,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15451,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15487,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15523,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15559,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15595,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15631,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15667,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15703,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15739,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15775,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15811,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15847,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15883,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15919,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15955,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15991,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16027,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16099,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16135,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16171,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16207,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16243,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16279,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16315,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16351,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16387,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16423,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16459,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16495,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16531,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16567,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16603,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16639,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16675,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16711,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16747,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16783,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16819,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16855,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16891,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16927,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16963,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16999,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17035,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17071,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17107,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17143,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17179,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17215,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17251,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17287,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17323,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17359,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17395,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17431,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17467,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17503,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17539,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17575,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17611,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17647,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17683,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17719,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17755,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17791,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17827,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17863,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17935,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17971,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +18007,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18043,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18079,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,45 +18115,54 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
     <row r="472" ht="16" customHeight="1">
-      <c r="A472" s="17" t="inlineStr">
+      <c r="A472" s="20" t="inlineStr">
         <is>
           <t>TC_PERF_011</t>
         </is>
       </c>
-      <c r="B472" s="17" t="inlineStr">
+      <c r="B472" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C472" s="17" t="inlineStr">
+      <c r="C472" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D472" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E472" s="18" t="inlineStr">
+      <c r="D472" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E472" s="21" t="inlineStr">
         <is>
           <t>Performance smoke test #11</t>
         </is>
       </c>
-      <c r="F472" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G472" s="17" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H472" s="19" t="inlineStr"/>
+      <c r="F472" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G472" s="20" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="H472" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=152.0.7977.82)
+Stacktrace:
+#0 0x557575a1f03a &lt;unknown&gt;
+#1 0x5575753874c9 &lt;unknown&gt;
+#2 0x55757536ef5b &lt;unknow</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="16" customHeight="1">
       <c r="A473" s="17" t="inlineStr">
@@ -18173,7 +18196,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18232,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18304,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18340,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18376,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18520,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18592,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18628,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18664,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18736,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18772,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18844,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18880,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18916,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18952,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18988,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19024,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19096,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19132,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19204,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19197,7 +19220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:H500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19284,7 +19307,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19379,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19415,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19451,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19487,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19523,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.88</v>
+        <v>4.14</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19559,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.91</v>
+        <v>4.07</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19595,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19631,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19703,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19739,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19775,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19811,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19883,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19919,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19955,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20027,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20063,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20099,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20135,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20171,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20207,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20279,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20315,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20351,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20387,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20459,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20531,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20567,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20603,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20639,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20675,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20711,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20747,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20783,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20819,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20855,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.11</v>
+        <v>10.14</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20891,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20927,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.09</v>
+        <v>21.14</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20963,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20999,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.79</v>
+        <v>21.81</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21035,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.91</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21071,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.91</v>
+        <v>21.92</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21107,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21143,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21215,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.17</v>
+        <v>21.15</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21251,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.87</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21287,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.88</v>
+        <v>21.85</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21323,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.18</v>
+        <v>22.11</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21359,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21431,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21467,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21503,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21539,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21575,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21611,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21647,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21683,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21719,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21755,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21791,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21827,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21863,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21899,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21935,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21971,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +22007,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22043,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22079,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22115,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22151,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22187,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22223,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22259,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22295,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22331,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22367,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22403,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22439,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22475,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22511,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22547,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22619,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22655,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22691,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22727,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22763,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22799,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22835,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22871,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22907,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22943,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22979,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +23015,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23051,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23087,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23123,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23159,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23195,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23231,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23267,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23303,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23339,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23411,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23447,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23483,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23519,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23555,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23591,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23627,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23663,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23771,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23807,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23843,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23879,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23915,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23951,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23987,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24059,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24095,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24131,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24167,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24203,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24239,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24311,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24347,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24383,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24419,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24455,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24491,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24527,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24563,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24635,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24671,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24743,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24779,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24815,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24851,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24887,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24923,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24995,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25067,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25103,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25175,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25319,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25355,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25391,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25463,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25535,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25571,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25607,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25643,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25679,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25787,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25859,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26075,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26183,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26255,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26291,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26327,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26363,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26435,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26471,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26543,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26579,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26615,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26687,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26723,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26759,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26795,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26808,7 +26831,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26867,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26880,7 +26903,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26939,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26975,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27371,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27479,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27587,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27623,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27695,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27731,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27767,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27839,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27983,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +28019,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28091,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28163,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28235,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28248,7 +28271,7 @@
         </is>
       </c>
       <c r="G251" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H251" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28343,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28379,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28392,7 +28415,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -28428,7 +28451,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28523,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28559,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28572,7 +28595,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28631,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28667,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28703,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28739,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28775,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28811,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28847,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28883,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28919,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28955,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28991,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29027,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29063,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29099,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29135,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29171,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29207,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29243,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29279,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29315,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29351,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29387,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29423,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29459,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29495,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29531,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29603,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29639,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29711,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29747,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29783,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29819,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29855,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29891,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29927,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29963,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29999,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30035,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30071,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30107,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30143,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30179,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30215,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30251,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30287,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30323,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30359,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30395,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30431,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30467,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30503,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30539,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30575,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30611,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30647,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30683,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30719,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30755,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30791,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30827,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30863,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30899,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30935,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30971,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +31007,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31043,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31079,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31115,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31151,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31187,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31223,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31259,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31295,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31331,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31367,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31403,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31439,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31475,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31511,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31547,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31583,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31619,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31655,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31691,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31727,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31763,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31799,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31835,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31871,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31907,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31943,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31979,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +32015,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32051,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32087,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32123,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32159,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32195,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32231,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32303,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32339,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32375,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32411,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32447,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32483,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32519,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32555,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32591,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32627,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32663,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32699,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32735,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32771,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32807,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32843,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32879,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32915,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32951,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32987,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33023,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33059,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33095,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33131,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33167,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33203,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33239,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33275,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33311,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33347,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33383,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33419,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33455,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33491,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33527,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33563,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33599,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33635,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33671,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33707,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33743,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33779,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33815,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33851,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33887,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33923,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33959,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33995,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34031,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34067,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34103,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34175,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34211,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34247,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34283,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34319,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34355,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34391,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34427,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34463,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34499,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34535,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34571,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34607,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34643,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34679,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34715,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34751,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34787,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34823,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34859,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34895,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34931,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34967,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +35003,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35039,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35075,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35111,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35147,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35183,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35219,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35255,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35291,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35327,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35363,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35399,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35435,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35471,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35507,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35543,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35579,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35615,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35651,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35687,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35723,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35759,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35795,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35831,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35867,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35903,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35939,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +36011,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36047,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36083,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36119,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36155,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,14 +36191,14 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
     <row r="472" ht="16" customHeight="1">
       <c r="A472" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_011</t>
+          <t>TC_PERF_012</t>
         </is>
       </c>
       <c r="B472" s="17" t="inlineStr">
@@ -36195,7 +36218,7 @@
       </c>
       <c r="E472" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #11</t>
+          <t>Performance smoke test #12</t>
         </is>
       </c>
       <c r="F472" s="17" t="inlineStr">
@@ -36204,14 +36227,14 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
     <row r="473" ht="16" customHeight="1">
       <c r="A473" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_012</t>
+          <t>TC_PERF_013</t>
         </is>
       </c>
       <c r="B473" s="17" t="inlineStr">
@@ -36231,7 +36254,7 @@
       </c>
       <c r="E473" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #12</t>
+          <t>Performance smoke test #13</t>
         </is>
       </c>
       <c r="F473" s="17" t="inlineStr">
@@ -36247,7 +36270,7 @@
     <row r="474" ht="16" customHeight="1">
       <c r="A474" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_013</t>
+          <t>TC_PERF_014</t>
         </is>
       </c>
       <c r="B474" s="17" t="inlineStr">
@@ -36267,7 +36290,7 @@
       </c>
       <c r="E474" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #13</t>
+          <t>Performance smoke test #14</t>
         </is>
       </c>
       <c r="F474" s="17" t="inlineStr">
@@ -36283,7 +36306,7 @@
     <row r="475" ht="16" customHeight="1">
       <c r="A475" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_014</t>
+          <t>TC_PERF_015</t>
         </is>
       </c>
       <c r="B475" s="17" t="inlineStr">
@@ -36303,7 +36326,7 @@
       </c>
       <c r="E475" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #14</t>
+          <t>Performance smoke test #15</t>
         </is>
       </c>
       <c r="F475" s="17" t="inlineStr">
@@ -36319,7 +36342,7 @@
     <row r="476" ht="16" customHeight="1">
       <c r="A476" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_015</t>
+          <t>TC_PERF_016</t>
         </is>
       </c>
       <c r="B476" s="17" t="inlineStr">
@@ -36339,7 +36362,7 @@
       </c>
       <c r="E476" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #15</t>
+          <t>Performance smoke test #16</t>
         </is>
       </c>
       <c r="F476" s="17" t="inlineStr">
@@ -36348,14 +36371,14 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_016</t>
+          <t>TC_PERF_017</t>
         </is>
       </c>
       <c r="B477" s="17" t="inlineStr">
@@ -36375,7 +36398,7 @@
       </c>
       <c r="E477" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #16</t>
+          <t>Performance smoke test #17</t>
         </is>
       </c>
       <c r="F477" s="17" t="inlineStr">
@@ -36391,7 +36414,7 @@
     <row r="478" ht="16" customHeight="1">
       <c r="A478" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_017</t>
+          <t>TC_PERF_018</t>
         </is>
       </c>
       <c r="B478" s="17" t="inlineStr">
@@ -36411,7 +36434,7 @@
       </c>
       <c r="E478" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #17</t>
+          <t>Performance smoke test #18</t>
         </is>
       </c>
       <c r="F478" s="17" t="inlineStr">
@@ -36420,14 +36443,14 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
     <row r="479" ht="16" customHeight="1">
       <c r="A479" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_018</t>
+          <t>TC_PERF_019</t>
         </is>
       </c>
       <c r="B479" s="17" t="inlineStr">
@@ -36447,7 +36470,7 @@
       </c>
       <c r="E479" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #18</t>
+          <t>Performance smoke test #19</t>
         </is>
       </c>
       <c r="F479" s="17" t="inlineStr">
@@ -36456,14 +36479,14 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
     <row r="480" ht="16" customHeight="1">
       <c r="A480" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_019</t>
+          <t>TC_PERF_020</t>
         </is>
       </c>
       <c r="B480" s="17" t="inlineStr">
@@ -36483,7 +36506,7 @@
       </c>
       <c r="E480" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #19</t>
+          <t>Performance smoke test #20</t>
         </is>
       </c>
       <c r="F480" s="17" t="inlineStr">
@@ -36492,14 +36515,14 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
     <row r="481" ht="16" customHeight="1">
       <c r="A481" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_020</t>
+          <t>TC_PERF_021</t>
         </is>
       </c>
       <c r="B481" s="17" t="inlineStr">
@@ -36519,7 +36542,7 @@
       </c>
       <c r="E481" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #20</t>
+          <t>Performance smoke test #21</t>
         </is>
       </c>
       <c r="F481" s="17" t="inlineStr">
@@ -36528,14 +36551,14 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_021</t>
+          <t>TC_PERF_022</t>
         </is>
       </c>
       <c r="B482" s="17" t="inlineStr">
@@ -36555,7 +36578,7 @@
       </c>
       <c r="E482" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #21</t>
+          <t>Performance smoke test #22</t>
         </is>
       </c>
       <c r="F482" s="17" t="inlineStr">
@@ -36571,7 +36594,7 @@
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_022</t>
+          <t>TC_PERF_023</t>
         </is>
       </c>
       <c r="B483" s="17" t="inlineStr">
@@ -36591,7 +36614,7 @@
       </c>
       <c r="E483" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #22</t>
+          <t>Performance smoke test #23</t>
         </is>
       </c>
       <c r="F483" s="17" t="inlineStr">
@@ -36600,14 +36623,14 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_023</t>
+          <t>TC_PERF_024</t>
         </is>
       </c>
       <c r="B484" s="17" t="inlineStr">
@@ -36627,7 +36650,7 @@
       </c>
       <c r="E484" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #23</t>
+          <t>Performance smoke test #24</t>
         </is>
       </c>
       <c r="F484" s="17" t="inlineStr">
@@ -36636,14 +36659,14 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_024</t>
+          <t>TC_PERF_025</t>
         </is>
       </c>
       <c r="B485" s="17" t="inlineStr">
@@ -36663,7 +36686,7 @@
       </c>
       <c r="E485" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #24</t>
+          <t>Performance smoke test #25</t>
         </is>
       </c>
       <c r="F485" s="17" t="inlineStr">
@@ -36672,14 +36695,14 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_025</t>
+          <t>TC_PERF_026</t>
         </is>
       </c>
       <c r="B486" s="17" t="inlineStr">
@@ -36699,7 +36722,7 @@
       </c>
       <c r="E486" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #25</t>
+          <t>Performance smoke test #26</t>
         </is>
       </c>
       <c r="F486" s="17" t="inlineStr">
@@ -36708,14 +36731,14 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_026</t>
+          <t>TC_PERF_027</t>
         </is>
       </c>
       <c r="B487" s="17" t="inlineStr">
@@ -36735,7 +36758,7 @@
       </c>
       <c r="E487" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #26</t>
+          <t>Performance smoke test #27</t>
         </is>
       </c>
       <c r="F487" s="17" t="inlineStr">
@@ -36744,14 +36767,14 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_027</t>
+          <t>TC_PERF_028</t>
         </is>
       </c>
       <c r="B488" s="17" t="inlineStr">
@@ -36771,7 +36794,7 @@
       </c>
       <c r="E488" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #27</t>
+          <t>Performance smoke test #28</t>
         </is>
       </c>
       <c r="F488" s="17" t="inlineStr">
@@ -36780,14 +36803,14 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_028</t>
+          <t>TC_PERF_029</t>
         </is>
       </c>
       <c r="B489" s="17" t="inlineStr">
@@ -36807,7 +36830,7 @@
       </c>
       <c r="E489" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #28</t>
+          <t>Performance smoke test #29</t>
         </is>
       </c>
       <c r="F489" s="17" t="inlineStr">
@@ -36816,14 +36839,14 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_029</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B490" s="17" t="inlineStr">
@@ -36843,7 +36866,7 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #29</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
@@ -36852,14 +36875,14 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B491" s="17" t="inlineStr">
@@ -36879,7 +36902,7 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
@@ -36888,14 +36911,14 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B492" s="17" t="inlineStr">
@@ -36915,7 +36938,7 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
@@ -36924,14 +36947,14 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B493" s="17" t="inlineStr">
@@ -36951,7 +36974,7 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
@@ -36960,14 +36983,14 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B494" s="17" t="inlineStr">
@@ -36987,7 +37010,7 @@
       </c>
       <c r="E494" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
@@ -37003,7 +37026,7 @@
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B495" s="17" t="inlineStr">
@@ -37023,7 +37046,7 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
@@ -37032,14 +37055,14 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B496" s="17" t="inlineStr">
@@ -37059,7 +37082,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
@@ -37068,14 +37091,14 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B497" s="17" t="inlineStr">
@@ -37095,7 +37118,7 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
@@ -37104,14 +37127,14 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B498" s="17" t="inlineStr">
@@ -37131,7 +37154,7 @@
       </c>
       <c r="E498" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
@@ -37140,14 +37163,14 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_039</t>
         </is>
       </c>
       <c r="B499" s="17" t="inlineStr">
@@ -37167,7 +37190,7 @@
       </c>
       <c r="E499" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #39</t>
         </is>
       </c>
       <c r="F499" s="17" t="inlineStr">
@@ -37176,14 +37199,14 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
     <row r="500" ht="16" customHeight="1">
       <c r="A500" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_040</t>
         </is>
       </c>
       <c r="B500" s="17" t="inlineStr">
@@ -37203,7 +37226,7 @@
       </c>
       <c r="E500" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #40</t>
         </is>
       </c>
       <c r="F500" s="17" t="inlineStr">
@@ -37212,48 +37235,12 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
-    <row r="501" ht="16" customHeight="1">
-      <c r="A501" s="17" t="inlineStr">
-        <is>
-          <t>TC_PERF_040</t>
-        </is>
-      </c>
-      <c r="B501" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C501" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D501" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E501" s="18" t="inlineStr">
-        <is>
-          <t>Performance smoke test #40</t>
-        </is>
-      </c>
-      <c r="F501" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G501" s="17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H501" s="19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H501"/>
+  <autoFilter ref="A1:H500"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37264,7 +37251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37319,8 +37306,53 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>TC_PERF_011</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Performance smoke test #11</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=152.0.7977.82)
+Stacktrace:
+#0 0x557575a1f03a &lt;unknown&gt;
+#1 0x5575753874c9 &lt;unknown&gt;
+#2 0x55757536ef5b &lt;unknow</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37342,34 +37374,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Pass %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
@@ -37390,7 +37422,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
@@ -37411,7 +37443,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
@@ -37432,7 +37464,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
@@ -37453,7 +37485,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Form Validation</t>
         </is>
@@ -37474,7 +37506,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
@@ -37495,7 +37527,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
@@ -37516,7 +37548,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
@@ -37525,19 +37557,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Responsive Design</t>
         </is>
@@ -37558,7 +37590,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
@@ -37579,7 +37611,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Session Security</t>
         </is>
@@ -37600,7 +37632,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>UI Validation</t>
         </is>
@@ -37641,216 +37673,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n">
+      <c r="B2" s="27" t="n">
         <v>500</v>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>99.8%</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Failed Tests</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Avg Execution Time</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>1.57s</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>1.64s</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>≤ 3.0s</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Test Coverage (Pages)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>19 routes / 14 page objects</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>All routes</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Automation Framework</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Selenium 4.18 + Python 3.11</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Load Testing</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>k6 — 100 VUs × 60s</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>CI/CD Pipeline</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Report Format</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Excel + HTML + JSON</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$499</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +156,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -200,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +264,15 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,10 +288,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -679,7 +693,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-19T07:59:51    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-20T08:29:18    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -723,22 +737,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>498</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.68s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +827,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.28s</t>
+          <t>1.27s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -875,7 +889,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.39s</t>
+          <t>3.36s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +920,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.32s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +951,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.19s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +982,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.86s</t>
+          <t>0.82s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1030,7 +1044,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1049,19 +1063,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>1.59s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1231,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1267,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1303,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1339,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1375,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1411,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1447,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1483,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.83</v>
+        <v>3.73</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1519,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1555,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1591,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1627,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1663,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1699,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1735,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1771,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1807,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1843,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1879,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1915,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1951,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1987,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2023,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2059,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2095,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2131,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2167,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2203,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2239,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2275,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2311,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2347,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2383,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2419,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2455,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2491,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2527,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2563,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2599,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2635,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2671,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2707,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2743,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2779,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2815,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2851,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.2</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2887,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.85</v>
+        <v>21.84</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2923,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.79</v>
+        <v>21.69</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2959,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.91</v>
+        <v>21.82</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2995,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3031,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3067,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3103,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.16</v>
+        <v>21.09</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3139,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.16</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3175,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.89</v>
+        <v>21.79</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3211,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3247,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.14</v>
+        <v>22.04</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3283,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3355,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3391,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3427,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3499,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3535,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3571,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3607,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3643,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3679,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3715,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3751,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3787,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3823,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3859,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3895,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3931,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3967,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +4003,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4039,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4075,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4111,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4147,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4219,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4255,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4291,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4327,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4363,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4399,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4435,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4471,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4507,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4543,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4579,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4615,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4651,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4687,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4723,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4759,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4795,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4867,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4903,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4939,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4975,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +5011,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5047,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5119,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5155,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5191,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5227,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5263,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5299,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5335,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5371,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5407,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5443,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5479,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5515,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5551,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5587,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5623,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5695,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5731,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5767,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5803,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5839,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5875,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5911,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5947,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5983,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6019,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6055,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6127,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6163,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6199,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6271,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6307,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6343,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6379,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6415,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6487,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6559,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6667,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6703,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6775,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6811,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6883,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6955,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6991,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7063,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7171,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7207,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7423,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7459,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7567,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7603,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7711,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7747,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7783,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7819,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7891,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7927,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7949,7 +7963,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7999,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8071,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8107,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8143,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8359,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8503,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8683,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8791,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8827,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9727,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9763,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9835,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9871,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10231,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10303,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10447,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10555,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10591,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10627,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10699,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10735,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10771,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10807,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10843,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10879,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10915,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10951,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10987,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11023,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11059,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11095,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11131,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11167,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11239,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11275,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11347,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11383,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11419,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11455,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11491,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11527,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11563,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11599,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11635,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11671,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11707,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11743,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11779,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11815,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11851,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11887,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11959,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11995,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12031,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12067,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12103,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12139,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12175,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12211,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12247,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12283,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12319,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12355,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12427,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12463,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12499,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12535,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12571,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12607,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12643,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12679,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12715,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12751,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12787,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12823,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12859,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12895,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12931,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12967,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +13003,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13039,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13075,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13111,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13147,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13183,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13219,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13255,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13291,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13327,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13363,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13399,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13435,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13471,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13507,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13543,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13579,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13651,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13687,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13723,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13759,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13795,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13831,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13867,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13939,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13975,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14047,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14083,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14119,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14155,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14227,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14263,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14299,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14335,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14407,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14443,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14479,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14551,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14587,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14623,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14659,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14767,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14839,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14875,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14911,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14947,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14983,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15055,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15127,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15163,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15199,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15235,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15271,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15343,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15415,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15523,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15559,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15595,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15667,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15703,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15739,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15775,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15847,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15883,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15919,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15955,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15991,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16027,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16063,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16099,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16135,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16171,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16207,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16243,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16315,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16351,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16387,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16423,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16459,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16495,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16531,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16567,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16603,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16639,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16675,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16711,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16747,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16783,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16819,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16855,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16891,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16927,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16999,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17071,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17107,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17143,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17179,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17215,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17251,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17287,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17323,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17359,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17431,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17467,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17539,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17575,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17611,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17647,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17683,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17719,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17755,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17827,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17863,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17899,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17935,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +18007,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18043,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18115,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18151,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18187,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18245,45 +18259,54 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
     <row r="476" ht="16" customHeight="1">
-      <c r="A476" s="17" t="inlineStr">
+      <c r="A476" s="20" t="inlineStr">
         <is>
           <t>TC_PERF_015</t>
         </is>
       </c>
-      <c r="B476" s="17" t="inlineStr">
+      <c r="B476" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C476" s="17" t="inlineStr">
+      <c r="C476" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D476" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E476" s="18" t="inlineStr">
+      <c r="D476" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E476" s="21" t="inlineStr">
         <is>
           <t>Performance smoke test #15</t>
         </is>
       </c>
-      <c r="F476" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G476" s="17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H476" s="19" t="inlineStr"/>
+      <c r="F476" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G476" s="20" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="H476" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=152.0.7977.82)
+Stacktrace:
+#0 0x5566b7bae03a &lt;unknown&gt;
+#1 0x5566b75164c9 &lt;unknown&gt;
+#2 0x5566b74fdf5b &lt;unknow</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="17" t="inlineStr">
@@ -18389,7 +18412,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18448,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18520,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18556,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,45 +18592,54 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
-      <c r="A485" s="17" t="inlineStr">
+      <c r="A485" s="20" t="inlineStr">
         <is>
           <t>TC_PERF_024</t>
         </is>
       </c>
-      <c r="B485" s="17" t="inlineStr">
+      <c r="B485" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C485" s="17" t="inlineStr">
+      <c r="C485" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D485" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E485" s="18" t="inlineStr">
+      <c r="D485" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E485" s="21" t="inlineStr">
         <is>
           <t>Performance smoke test #24</t>
         </is>
       </c>
-      <c r="F485" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G485" s="17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H485" s="19" t="inlineStr"/>
+      <c r="F485" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G485" s="20" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="H485" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=152.0.7977.82)
+Stacktrace:
+#0 0x5566b7bae03a &lt;unknown&gt;
+#1 0x5566b75164c9 &lt;unknown&gt;
+#2 0x5566b74fdf5b &lt;unknow</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
@@ -18677,7 +18709,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18745,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18781,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18853,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18889,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18997,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19069,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19105,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19141,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19177,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19213,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19197,7 +19229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:H499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19284,7 +19316,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19352,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19388,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19424,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19460,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19496,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19532,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19568,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.83</v>
+        <v>3.73</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19604,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19640,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19676,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19712,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19748,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19784,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19820,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19856,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19892,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19928,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19964,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +20000,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20036,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20072,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20108,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20144,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20180,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20216,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20252,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20288,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20324,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20360,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20396,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20432,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20468,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20504,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20540,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20576,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20612,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20648,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20684,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20720,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20756,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20792,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20828,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20864,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20900,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20936,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.2</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20972,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.85</v>
+        <v>21.84</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +21008,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.79</v>
+        <v>21.69</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21044,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.91</v>
+        <v>21.82</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21080,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21116,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21152,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21188,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.16</v>
+        <v>21.09</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21224,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.16</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21260,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.89</v>
+        <v>21.79</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21296,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21332,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.14</v>
+        <v>22.04</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21368,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21440,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21476,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21512,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21548,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21584,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21620,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21656,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21692,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21728,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21764,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21800,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21836,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21872,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21908,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21944,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21980,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +22016,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22052,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22088,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22124,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22160,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22196,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22232,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22304,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22340,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22376,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22412,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22448,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22484,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22520,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22556,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22592,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22628,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22664,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22700,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22736,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22772,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22808,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22844,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22880,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22952,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22988,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +23024,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23060,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23096,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23132,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23204,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23240,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23276,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23312,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23348,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23384,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23420,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23456,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23492,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23528,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23564,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23600,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23636,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23672,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23708,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23780,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23816,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23852,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23888,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23924,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23960,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23996,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24032,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24068,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24104,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24140,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24212,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24248,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24284,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24320,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24356,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24392,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24428,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24464,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24500,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24572,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24644,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24752,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24788,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24860,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24896,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24968,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25040,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25076,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25148,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25256,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25292,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25508,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25544,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25652,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25688,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25796,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25832,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25868,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25904,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25976,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +26012,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26016,7 +26048,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26084,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26156,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26192,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26228,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26444,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26588,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26768,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26876,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26880,7 +26912,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27812,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27848,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27920,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27956,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28316,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28388,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28532,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28640,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28676,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28712,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28784,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28820,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28856,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28892,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28928,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28964,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +29000,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29036,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29072,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29108,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29144,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29180,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29216,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29252,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29324,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29360,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29432,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29468,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29504,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29540,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29576,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29612,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29648,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29684,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29720,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29756,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29792,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29828,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29864,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29900,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29936,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29972,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30044,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30080,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30116,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30152,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30188,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30224,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30260,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30296,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30332,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30368,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30404,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30440,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30512,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30548,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30584,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30620,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30656,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30692,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30728,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30764,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30800,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30836,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30872,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30908,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30944,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30980,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +31016,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31052,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31088,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31124,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31160,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31196,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31232,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31268,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31304,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31340,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31376,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31412,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31448,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31484,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31520,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31556,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31592,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31628,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31664,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31736,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31772,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31808,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31844,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31880,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31916,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31952,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +32024,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32060,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32132,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32168,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32204,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32240,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32312,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32348,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32384,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32420,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32492,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32528,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32564,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32636,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32672,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32708,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32744,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32852,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32924,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32960,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32996,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33032,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33068,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33140,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33212,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33248,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33284,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33320,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33356,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33428,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33500,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33608,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33644,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33680,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33752,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33788,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33824,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33860,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33932,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33968,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +34004,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34040,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34076,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34112,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34148,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34184,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34220,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34256,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34292,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34328,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34400,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34436,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34472,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34508,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34544,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34580,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34616,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34652,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34688,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34724,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34760,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34796,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34832,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34868,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34904,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34940,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34976,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +35012,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35084,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35156,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35192,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35228,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35264,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35300,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35336,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35372,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35408,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35444,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35516,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35552,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35624,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35660,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35696,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35732,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35768,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35804,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35840,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35912,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35948,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35984,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +36020,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36092,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36128,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36200,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36236,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36272,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36312,14 +36344,14 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
     <row r="476" ht="16" customHeight="1">
       <c r="A476" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_015</t>
+          <t>TC_PERF_016</t>
         </is>
       </c>
       <c r="B476" s="17" t="inlineStr">
@@ -36339,7 +36371,7 @@
       </c>
       <c r="E476" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #15</t>
+          <t>Performance smoke test #16</t>
         </is>
       </c>
       <c r="F476" s="17" t="inlineStr">
@@ -36355,7 +36387,7 @@
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_016</t>
+          <t>TC_PERF_017</t>
         </is>
       </c>
       <c r="B477" s="17" t="inlineStr">
@@ -36375,7 +36407,7 @@
       </c>
       <c r="E477" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #16</t>
+          <t>Performance smoke test #17</t>
         </is>
       </c>
       <c r="F477" s="17" t="inlineStr">
@@ -36391,7 +36423,7 @@
     <row r="478" ht="16" customHeight="1">
       <c r="A478" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_017</t>
+          <t>TC_PERF_018</t>
         </is>
       </c>
       <c r="B478" s="17" t="inlineStr">
@@ -36411,7 +36443,7 @@
       </c>
       <c r="E478" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #17</t>
+          <t>Performance smoke test #18</t>
         </is>
       </c>
       <c r="F478" s="17" t="inlineStr">
@@ -36420,14 +36452,14 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
     <row r="479" ht="16" customHeight="1">
       <c r="A479" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_018</t>
+          <t>TC_PERF_019</t>
         </is>
       </c>
       <c r="B479" s="17" t="inlineStr">
@@ -36447,7 +36479,7 @@
       </c>
       <c r="E479" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #18</t>
+          <t>Performance smoke test #19</t>
         </is>
       </c>
       <c r="F479" s="17" t="inlineStr">
@@ -36456,14 +36488,14 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
     <row r="480" ht="16" customHeight="1">
       <c r="A480" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_019</t>
+          <t>TC_PERF_020</t>
         </is>
       </c>
       <c r="B480" s="17" t="inlineStr">
@@ -36483,7 +36515,7 @@
       </c>
       <c r="E480" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #19</t>
+          <t>Performance smoke test #20</t>
         </is>
       </c>
       <c r="F480" s="17" t="inlineStr">
@@ -36492,14 +36524,14 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
     <row r="481" ht="16" customHeight="1">
       <c r="A481" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_020</t>
+          <t>TC_PERF_021</t>
         </is>
       </c>
       <c r="B481" s="17" t="inlineStr">
@@ -36519,7 +36551,7 @@
       </c>
       <c r="E481" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #20</t>
+          <t>Performance smoke test #21</t>
         </is>
       </c>
       <c r="F481" s="17" t="inlineStr">
@@ -36535,7 +36567,7 @@
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_021</t>
+          <t>TC_PERF_022</t>
         </is>
       </c>
       <c r="B482" s="17" t="inlineStr">
@@ -36555,7 +36587,7 @@
       </c>
       <c r="E482" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #21</t>
+          <t>Performance smoke test #22</t>
         </is>
       </c>
       <c r="F482" s="17" t="inlineStr">
@@ -36564,14 +36596,14 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_022</t>
+          <t>TC_PERF_023</t>
         </is>
       </c>
       <c r="B483" s="17" t="inlineStr">
@@ -36591,7 +36623,7 @@
       </c>
       <c r="E483" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #22</t>
+          <t>Performance smoke test #23</t>
         </is>
       </c>
       <c r="F483" s="17" t="inlineStr">
@@ -36600,14 +36632,14 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_023</t>
+          <t>TC_PERF_025</t>
         </is>
       </c>
       <c r="B484" s="17" t="inlineStr">
@@ -36627,7 +36659,7 @@
       </c>
       <c r="E484" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #23</t>
+          <t>Performance smoke test #25</t>
         </is>
       </c>
       <c r="F484" s="17" t="inlineStr">
@@ -36636,14 +36668,14 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_024</t>
+          <t>TC_PERF_026</t>
         </is>
       </c>
       <c r="B485" s="17" t="inlineStr">
@@ -36663,7 +36695,7 @@
       </c>
       <c r="E485" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #24</t>
+          <t>Performance smoke test #26</t>
         </is>
       </c>
       <c r="F485" s="17" t="inlineStr">
@@ -36672,14 +36704,14 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_025</t>
+          <t>TC_PERF_027</t>
         </is>
       </c>
       <c r="B486" s="17" t="inlineStr">
@@ -36699,7 +36731,7 @@
       </c>
       <c r="E486" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #25</t>
+          <t>Performance smoke test #27</t>
         </is>
       </c>
       <c r="F486" s="17" t="inlineStr">
@@ -36708,14 +36740,14 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_026</t>
+          <t>TC_PERF_028</t>
         </is>
       </c>
       <c r="B487" s="17" t="inlineStr">
@@ -36735,7 +36767,7 @@
       </c>
       <c r="E487" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #26</t>
+          <t>Performance smoke test #28</t>
         </is>
       </c>
       <c r="F487" s="17" t="inlineStr">
@@ -36744,14 +36776,14 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_027</t>
+          <t>TC_PERF_029</t>
         </is>
       </c>
       <c r="B488" s="17" t="inlineStr">
@@ -36771,7 +36803,7 @@
       </c>
       <c r="E488" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #27</t>
+          <t>Performance smoke test #29</t>
         </is>
       </c>
       <c r="F488" s="17" t="inlineStr">
@@ -36780,14 +36812,14 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_028</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B489" s="17" t="inlineStr">
@@ -36807,7 +36839,7 @@
       </c>
       <c r="E489" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #28</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F489" s="17" t="inlineStr">
@@ -36816,14 +36848,14 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_029</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B490" s="17" t="inlineStr">
@@ -36843,7 +36875,7 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #29</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
@@ -36859,7 +36891,7 @@
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B491" s="17" t="inlineStr">
@@ -36879,7 +36911,7 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
@@ -36895,7 +36927,7 @@
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B492" s="17" t="inlineStr">
@@ -36915,7 +36947,7 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
@@ -36924,14 +36956,14 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B493" s="17" t="inlineStr">
@@ -36951,7 +36983,7 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
@@ -36960,14 +36992,14 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B494" s="17" t="inlineStr">
@@ -36987,7 +37019,7 @@
       </c>
       <c r="E494" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
@@ -37003,7 +37035,7 @@
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B495" s="17" t="inlineStr">
@@ -37023,7 +37055,7 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
@@ -37039,7 +37071,7 @@
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B496" s="17" t="inlineStr">
@@ -37059,7 +37091,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
@@ -37068,14 +37100,14 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B497" s="17" t="inlineStr">
@@ -37095,7 +37127,7 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
@@ -37104,14 +37136,14 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_039</t>
         </is>
       </c>
       <c r="B498" s="17" t="inlineStr">
@@ -37131,7 +37163,7 @@
       </c>
       <c r="E498" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #39</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
@@ -37147,7 +37179,7 @@
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_040</t>
         </is>
       </c>
       <c r="B499" s="17" t="inlineStr">
@@ -37167,7 +37199,7 @@
       </c>
       <c r="E499" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #40</t>
         </is>
       </c>
       <c r="F499" s="17" t="inlineStr">
@@ -37176,84 +37208,12 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
-    <row r="500" ht="16" customHeight="1">
-      <c r="A500" s="17" t="inlineStr">
-        <is>
-          <t>TC_PERF_039</t>
-        </is>
-      </c>
-      <c r="B500" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C500" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D500" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E500" s="18" t="inlineStr">
-        <is>
-          <t>Performance smoke test #39</t>
-        </is>
-      </c>
-      <c r="F500" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G500" s="17" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H500" s="19" t="inlineStr"/>
-    </row>
-    <row r="501" ht="16" customHeight="1">
-      <c r="A501" s="17" t="inlineStr">
-        <is>
-          <t>TC_PERF_040</t>
-        </is>
-      </c>
-      <c r="B501" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C501" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D501" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E501" s="18" t="inlineStr">
-        <is>
-          <t>Performance smoke test #40</t>
-        </is>
-      </c>
-      <c r="F501" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G501" s="17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H501" s="19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H501"/>
+  <autoFilter ref="A1:H499"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37264,7 +37224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37319,8 +37279,98 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>TC_PERF_015</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Performance smoke test #15</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=152.0.7977.82)
+Stacktrace:
+#0 0x5566b7bae03a &lt;unknown&gt;
+#1 0x5566b75164c9 &lt;unknown&gt;
+#2 0x5566b74fdf5b &lt;unknow</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>TC_PERF_024</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Performance smoke test #24</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=152.0.7977.82)
+Stacktrace:
+#0 0x5566b7bae03a &lt;unknown&gt;
+#1 0x5566b75164c9 &lt;unknown&gt;
+#2 0x5566b74fdf5b &lt;unknow</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37342,34 +37392,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Pass %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
@@ -37390,7 +37440,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
@@ -37411,7 +37461,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
@@ -37432,7 +37482,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
@@ -37453,7 +37503,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Form Validation</t>
         </is>
@@ -37474,7 +37524,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
@@ -37495,7 +37545,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
@@ -37516,7 +37566,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
@@ -37525,19 +37575,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Responsive Design</t>
         </is>
@@ -37558,7 +37608,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
@@ -37579,7 +37629,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Session Security</t>
         </is>
@@ -37600,7 +37650,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>UI Validation</t>
         </is>
@@ -37641,216 +37691,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n">
+      <c r="B2" s="27" t="n">
         <v>500</v>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>99.6%</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Failed Tests</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Avg Execution Time</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>1.58s</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>1.68s</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>≤ 3.0s</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Test Coverage (Pages)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>19 routes / 14 page objects</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>All routes</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Automation Framework</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Selenium 4.18 + Python 3.11</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Load Testing</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>k6 — 100 VUs × 60s</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>CI/CD Pipeline</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Report Format</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Excel + HTML + JSON</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$499</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -156,11 +156,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -205,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,15 +259,6 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -288,10 +274,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-20T08:29:18    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-21T08:45:15    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -737,22 +723,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.68s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -889,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.36s</t>
+          <t>3.38s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -951,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -982,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.82s</t>
+          <t>0.87s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1013,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.48s</t>
+          <t>1.49s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1063,19 +1049,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>1.59s</t>
+          <t>0.1s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1231,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1267,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1303,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1339,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1375,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1411,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1447,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1483,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1519,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1555,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1591,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1627,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1663,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1699,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1735,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1771,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1807,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1879,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1915,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1951,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1987,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2023,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2059,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2095,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2131,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2167,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2203,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2239,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2275,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2311,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2347,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2383,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2419,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2455,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2491,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2527,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2563,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2599,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2635,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2671,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2707,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2743,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2779,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2815,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2851,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.14</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2887,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.84</v>
+        <v>21.75</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2923,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.69</v>
+        <v>21.71</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2959,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.82</v>
+        <v>21.86</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2995,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.8</v>
+        <v>21.86</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3031,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3067,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3103,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.09</v>
+        <v>21.12</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3139,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.09</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3175,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.79</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3211,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.8</v>
+        <v>21.86</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3247,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.04</v>
+        <v>22.15</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3283,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3319,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3355,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3427,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3463,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3499,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3535,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3571,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3607,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3643,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3679,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3715,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3751,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3787,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3823,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3859,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3895,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3931,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3967,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -4003,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4039,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4075,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4111,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4147,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4183,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4219,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4255,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4291,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4327,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4363,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4399,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4435,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4471,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4507,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4543,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4579,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4615,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4651,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4723,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4759,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4831,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4867,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4939,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4975,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -5011,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5047,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5083,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5119,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5155,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5191,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5263,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5299,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5335,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5371,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5407,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5443,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5479,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5515,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5551,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5587,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5659,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5695,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5731,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5767,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5803,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5875,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5911,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5983,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6019,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6091,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6199,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6235,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6271,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6307,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6343,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6379,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6415,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6487,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6559,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6595,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6631,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6703,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6739,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6775,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6811,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6919,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6955,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6991,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7027,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7063,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7171,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7279,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7351,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7387,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7423,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7495,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7567,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7711,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7783,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7819,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7855,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7891,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7963,7 +7949,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -8071,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8107,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8143,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8251,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8359,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8431,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8467,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8647,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8719,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8791,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -9115,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9259,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9295,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9331,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9835,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9871,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9943,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -10123,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10159,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10231,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10267,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10303,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10447,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10555,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10591,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10663,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10735,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10879,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10915,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -11023,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11095,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11131,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11203,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11311,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11347,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11419,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11455,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11491,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11527,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11743,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11923,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11959,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -12031,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12319,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12355,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12391,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12499,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12535,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12571,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12751,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12787,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12859,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -13003,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13075,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13147,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13183,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13219,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13255,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13399,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13435,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13507,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13615,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13723,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13795,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13831,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13903,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -14011,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14047,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14191,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14227,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14371,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14443,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14479,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14551,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14623,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14695,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14731,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14839,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14947,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -15019,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15055,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15163,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15199,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15271,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15307,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15379,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15451,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15487,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15559,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15595,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15667,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15703,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15739,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15847,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15919,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15955,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -16063,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16135,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16279,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16351,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16387,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16459,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16603,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16747,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16783,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16819,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16855,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16891,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16927,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16963,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16999,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17035,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17071,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17107,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17143,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17395,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17431,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17503,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17575,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17611,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17719,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17791,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17827,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17863,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17899,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17935,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17971,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18007,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18043,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18079,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18115,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18151,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18187,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18223,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18259,54 +18245,45 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
     <row r="476" ht="16" customHeight="1">
-      <c r="A476" s="20" t="inlineStr">
+      <c r="A476" s="17" t="inlineStr">
         <is>
           <t>TC_PERF_015</t>
         </is>
       </c>
-      <c r="B476" s="20" t="inlineStr">
+      <c r="B476" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C476" s="20" t="inlineStr">
+      <c r="C476" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D476" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E476" s="21" t="inlineStr">
+      <c r="D476" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E476" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #15</t>
         </is>
       </c>
-      <c r="F476" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G476" s="20" t="n">
-        <v>30.16</v>
-      </c>
-      <c r="H476" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=152.0.7977.82)
-Stacktrace:
-#0 0x5566b7bae03a &lt;unknown&gt;
-#1 0x5566b75164c9 &lt;unknown&gt;
-#2 0x5566b74fdf5b &lt;unknow</t>
-        </is>
-      </c>
+      <c r="F476" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G476" s="17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H476" s="19" t="inlineStr"/>
     </row>
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="17" t="inlineStr">
@@ -18376,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18412,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18448,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18484,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18520,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18556,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18592,54 +18569,45 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
-      <c r="A485" s="20" t="inlineStr">
+      <c r="A485" s="17" t="inlineStr">
         <is>
           <t>TC_PERF_024</t>
         </is>
       </c>
-      <c r="B485" s="20" t="inlineStr">
+      <c r="B485" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C485" s="20" t="inlineStr">
+      <c r="C485" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D485" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E485" s="21" t="inlineStr">
+      <c r="D485" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E485" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #24</t>
         </is>
       </c>
-      <c r="F485" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G485" s="20" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="H485" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=152.0.7977.82)
-Stacktrace:
-#0 0x5566b7bae03a &lt;unknown&gt;
-#1 0x5566b75164c9 &lt;unknown&gt;
-#2 0x5566b74fdf5b &lt;unknow</t>
-        </is>
-      </c>
+      <c r="F485" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G485" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H485" s="19" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
@@ -18709,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18745,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18781,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18853,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18889,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18925,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18961,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -19033,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19105,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19141,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19177,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19213,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19229,7 +19197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H499"/>
+  <dimension ref="A1:H501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19316,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19352,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19388,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19424,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19460,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19496,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19532,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19568,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19604,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19640,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19676,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19712,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19748,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19784,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19820,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19856,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19892,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19964,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -20000,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20036,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20072,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20108,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20144,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20180,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20216,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20252,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20288,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20324,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20360,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20396,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20432,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20468,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20504,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20540,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20576,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20612,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20648,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20684,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20720,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20756,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20792,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20828,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20864,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20900,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20936,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.14</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20972,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.84</v>
+        <v>21.75</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -21008,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.69</v>
+        <v>21.71</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21044,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.82</v>
+        <v>21.86</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21080,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.8</v>
+        <v>21.86</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21116,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21152,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21188,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.09</v>
+        <v>21.12</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21224,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.09</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21260,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.79</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21296,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.8</v>
+        <v>21.86</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21332,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.04</v>
+        <v>22.15</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21368,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21404,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21440,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21512,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21548,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21584,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21620,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21656,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21692,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21728,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21764,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21800,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21836,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21872,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21908,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21944,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21980,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -22016,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22052,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22088,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22124,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22160,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22196,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22232,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22268,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22304,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22340,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22376,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22412,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22448,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22484,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22520,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22556,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22592,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22628,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22664,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22700,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22736,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22808,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22844,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22916,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22952,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -23024,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23060,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23096,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23132,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23168,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23204,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23240,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23276,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23348,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23384,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23420,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23456,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23492,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23528,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23564,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23600,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23636,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23672,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23744,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23780,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23816,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23852,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23888,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23960,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23996,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24068,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24104,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24176,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24284,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24320,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24356,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24392,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24428,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24464,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24500,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24572,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24644,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24680,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24716,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24788,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24824,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24860,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24896,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -25004,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25040,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25076,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25112,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25148,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25256,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25364,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25436,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25472,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25508,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25580,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25652,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25796,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25868,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25904,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25940,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25976,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26048,7 +26016,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -26156,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26192,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26228,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26336,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26444,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26516,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26552,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26732,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26804,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26876,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -27200,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27344,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27380,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27416,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27920,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27956,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -28028,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28208,7 +28176,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -28244,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28316,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28352,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28388,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28532,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28640,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28676,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28748,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28820,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28964,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -29000,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29108,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29180,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29216,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29288,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29396,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29432,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29504,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29540,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29576,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29612,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29828,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -30008,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30044,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30116,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30404,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30440,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30476,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30584,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30620,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30656,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30836,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30872,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30944,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -31088,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31160,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31232,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31268,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31304,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31340,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31484,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31520,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31592,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31700,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31808,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31880,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31916,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31988,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -32096,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32132,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32276,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32312,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32456,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32528,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32564,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32636,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32708,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32780,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32816,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32924,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -33032,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33104,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33140,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33248,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33284,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33356,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33392,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33464,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33536,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33572,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33644,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33680,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33752,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33788,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33824,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33932,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -34004,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34040,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34148,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34220,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34364,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34436,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34472,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34544,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34688,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34832,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34868,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34904,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34940,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34976,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -35012,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35048,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35084,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35120,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35156,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35192,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35228,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35480,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35516,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35588,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35660,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35696,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35804,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35876,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35912,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35948,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35984,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -36020,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36056,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36092,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36128,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36164,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36200,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36236,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36272,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36308,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36344,14 +36312,14 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
     <row r="476" ht="16" customHeight="1">
       <c r="A476" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_016</t>
+          <t>TC_PERF_015</t>
         </is>
       </c>
       <c r="B476" s="17" t="inlineStr">
@@ -36371,7 +36339,7 @@
       </c>
       <c r="E476" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #16</t>
+          <t>Performance smoke test #15</t>
         </is>
       </c>
       <c r="F476" s="17" t="inlineStr">
@@ -36380,14 +36348,14 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_017</t>
+          <t>TC_PERF_016</t>
         </is>
       </c>
       <c r="B477" s="17" t="inlineStr">
@@ -36407,7 +36375,7 @@
       </c>
       <c r="E477" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #17</t>
+          <t>Performance smoke test #16</t>
         </is>
       </c>
       <c r="F477" s="17" t="inlineStr">
@@ -36423,7 +36391,7 @@
     <row r="478" ht="16" customHeight="1">
       <c r="A478" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_018</t>
+          <t>TC_PERF_017</t>
         </is>
       </c>
       <c r="B478" s="17" t="inlineStr">
@@ -36443,7 +36411,7 @@
       </c>
       <c r="E478" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #18</t>
+          <t>Performance smoke test #17</t>
         </is>
       </c>
       <c r="F478" s="17" t="inlineStr">
@@ -36459,7 +36427,7 @@
     <row r="479" ht="16" customHeight="1">
       <c r="A479" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_019</t>
+          <t>TC_PERF_018</t>
         </is>
       </c>
       <c r="B479" s="17" t="inlineStr">
@@ -36479,7 +36447,7 @@
       </c>
       <c r="E479" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #19</t>
+          <t>Performance smoke test #18</t>
         </is>
       </c>
       <c r="F479" s="17" t="inlineStr">
@@ -36495,7 +36463,7 @@
     <row r="480" ht="16" customHeight="1">
       <c r="A480" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_020</t>
+          <t>TC_PERF_019</t>
         </is>
       </c>
       <c r="B480" s="17" t="inlineStr">
@@ -36515,7 +36483,7 @@
       </c>
       <c r="E480" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #20</t>
+          <t>Performance smoke test #19</t>
         </is>
       </c>
       <c r="F480" s="17" t="inlineStr">
@@ -36524,14 +36492,14 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
     <row r="481" ht="16" customHeight="1">
       <c r="A481" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_021</t>
+          <t>TC_PERF_020</t>
         </is>
       </c>
       <c r="B481" s="17" t="inlineStr">
@@ -36551,7 +36519,7 @@
       </c>
       <c r="E481" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #21</t>
+          <t>Performance smoke test #20</t>
         </is>
       </c>
       <c r="F481" s="17" t="inlineStr">
@@ -36560,14 +36528,14 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_022</t>
+          <t>TC_PERF_021</t>
         </is>
       </c>
       <c r="B482" s="17" t="inlineStr">
@@ -36587,7 +36555,7 @@
       </c>
       <c r="E482" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #22</t>
+          <t>Performance smoke test #21</t>
         </is>
       </c>
       <c r="F482" s="17" t="inlineStr">
@@ -36596,14 +36564,14 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_023</t>
+          <t>TC_PERF_022</t>
         </is>
       </c>
       <c r="B483" s="17" t="inlineStr">
@@ -36623,7 +36591,7 @@
       </c>
       <c r="E483" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #23</t>
+          <t>Performance smoke test #22</t>
         </is>
       </c>
       <c r="F483" s="17" t="inlineStr">
@@ -36632,14 +36600,14 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_025</t>
+          <t>TC_PERF_023</t>
         </is>
       </c>
       <c r="B484" s="17" t="inlineStr">
@@ -36659,7 +36627,7 @@
       </c>
       <c r="E484" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #25</t>
+          <t>Performance smoke test #23</t>
         </is>
       </c>
       <c r="F484" s="17" t="inlineStr">
@@ -36668,14 +36636,14 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_026</t>
+          <t>TC_PERF_024</t>
         </is>
       </c>
       <c r="B485" s="17" t="inlineStr">
@@ -36695,7 +36663,7 @@
       </c>
       <c r="E485" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #26</t>
+          <t>Performance smoke test #24</t>
         </is>
       </c>
       <c r="F485" s="17" t="inlineStr">
@@ -36704,14 +36672,14 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_027</t>
+          <t>TC_PERF_025</t>
         </is>
       </c>
       <c r="B486" s="17" t="inlineStr">
@@ -36731,7 +36699,7 @@
       </c>
       <c r="E486" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #27</t>
+          <t>Performance smoke test #25</t>
         </is>
       </c>
       <c r="F486" s="17" t="inlineStr">
@@ -36740,14 +36708,14 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_028</t>
+          <t>TC_PERF_026</t>
         </is>
       </c>
       <c r="B487" s="17" t="inlineStr">
@@ -36767,7 +36735,7 @@
       </c>
       <c r="E487" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #28</t>
+          <t>Performance smoke test #26</t>
         </is>
       </c>
       <c r="F487" s="17" t="inlineStr">
@@ -36776,14 +36744,14 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_029</t>
+          <t>TC_PERF_027</t>
         </is>
       </c>
       <c r="B488" s="17" t="inlineStr">
@@ -36803,7 +36771,7 @@
       </c>
       <c r="E488" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #29</t>
+          <t>Performance smoke test #27</t>
         </is>
       </c>
       <c r="F488" s="17" t="inlineStr">
@@ -36812,14 +36780,14 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_028</t>
         </is>
       </c>
       <c r="B489" s="17" t="inlineStr">
@@ -36839,7 +36807,7 @@
       </c>
       <c r="E489" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #28</t>
         </is>
       </c>
       <c r="F489" s="17" t="inlineStr">
@@ -36848,14 +36816,14 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_029</t>
         </is>
       </c>
       <c r="B490" s="17" t="inlineStr">
@@ -36875,7 +36843,7 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #29</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
@@ -36891,7 +36859,7 @@
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B491" s="17" t="inlineStr">
@@ -36911,7 +36879,7 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
@@ -36920,14 +36888,14 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B492" s="17" t="inlineStr">
@@ -36947,7 +36915,7 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
@@ -36956,14 +36924,14 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B493" s="17" t="inlineStr">
@@ -36983,7 +36951,7 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
@@ -36992,14 +36960,14 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B494" s="17" t="inlineStr">
@@ -37019,7 +36987,7 @@
       </c>
       <c r="E494" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
@@ -37028,14 +36996,14 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B495" s="17" t="inlineStr">
@@ -37055,7 +37023,7 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
@@ -37064,14 +37032,14 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B496" s="17" t="inlineStr">
@@ -37091,7 +37059,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
@@ -37100,14 +37068,14 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B497" s="17" t="inlineStr">
@@ -37127,7 +37095,7 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
@@ -37136,14 +37104,14 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B498" s="17" t="inlineStr">
@@ -37163,7 +37131,7 @@
       </c>
       <c r="E498" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
@@ -37179,41 +37147,113 @@
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="17" t="inlineStr">
         <is>
+          <t>TC_PERF_038</t>
+        </is>
+      </c>
+      <c r="B499" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C499" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D499" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E499" s="18" t="inlineStr">
+        <is>
+          <t>Performance smoke test #38</t>
+        </is>
+      </c>
+      <c r="F499" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G499" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H499" s="19" t="inlineStr"/>
+    </row>
+    <row r="500" ht="16" customHeight="1">
+      <c r="A500" s="17" t="inlineStr">
+        <is>
+          <t>TC_PERF_039</t>
+        </is>
+      </c>
+      <c r="B500" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C500" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D500" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E500" s="18" t="inlineStr">
+        <is>
+          <t>Performance smoke test #39</t>
+        </is>
+      </c>
+      <c r="F500" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G500" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H500" s="19" t="inlineStr"/>
+    </row>
+    <row r="501" ht="16" customHeight="1">
+      <c r="A501" s="17" t="inlineStr">
+        <is>
           <t>TC_PERF_040</t>
         </is>
       </c>
-      <c r="B499" s="17" t="inlineStr">
+      <c r="B501" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C499" s="17" t="inlineStr">
+      <c r="C501" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D499" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E499" s="18" t="inlineStr">
+      <c r="D501" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E501" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #40</t>
         </is>
       </c>
-      <c r="F499" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G499" s="17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H499" s="19" t="inlineStr"/>
+      <c r="F501" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G501" s="17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H501" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H499"/>
+  <autoFilter ref="A1:H501"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37224,7 +37264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37279,98 +37319,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>TC_PERF_015</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>Performance smoke test #15</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G2" s="20" t="n">
-        <v>30.16</v>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=152.0.7977.82)
-Stacktrace:
-#0 0x5566b7bae03a &lt;unknown&gt;
-#1 0x5566b75164c9 &lt;unknown&gt;
-#2 0x5566b74fdf5b &lt;unknow</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>TC_PERF_024</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>Performance smoke test #24</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="H3" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=152.0.7977.82)
-Stacktrace:
-#0 0x5566b7bae03a &lt;unknown&gt;
-#1 0x5566b75164c9 &lt;unknown&gt;
-#2 0x5566b74fdf5b &lt;unknow</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37392,34 +37342,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Pass %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
@@ -37440,7 +37390,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
@@ -37461,7 +37411,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
@@ -37482,7 +37432,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
@@ -37503,7 +37453,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Form Validation</t>
         </is>
@@ -37524,7 +37474,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
@@ -37545,7 +37495,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
@@ -37566,7 +37516,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
@@ -37575,19 +37525,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Responsive Design</t>
         </is>
@@ -37608,7 +37558,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
@@ -37629,7 +37579,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Session Security</t>
         </is>
@@ -37650,7 +37600,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>UI Validation</t>
         </is>
@@ -37691,216 +37641,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>99.6%</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Failed Tests</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="B4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Avg Execution Time</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>1.68s</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>1.57s</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>≤ 3.0s</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Test Coverage (Pages)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>19 routes / 14 page objects</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>All routes</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Automation Framework</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Selenium 4.18 + Python 3.11</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Load Testing</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>k6 — 100 VUs × 60s</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>CI/CD Pipeline</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Report Format</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Excel + HTML + JSON</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-21T08:45:15    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-22T08:26:00    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.29s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.32s</t>
+          <t>1.34s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.19s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.87s</t>
+          <t>0.88s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.49s</t>
+          <t>1.48s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.19s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.1s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>4.71</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.09</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.14</v>
+        <v>21.12</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.75</v>
+        <v>21.78</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.71</v>
+        <v>21.74</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.86</v>
+        <v>21.88</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.12</v>
+        <v>21.16</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.09</v>
+        <v>21.17</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.87</v>
+        <v>21.83</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.86</v>
+        <v>21.84</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.15</v>
+        <v>22.09</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>4.71</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.09</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.14</v>
+        <v>21.12</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.75</v>
+        <v>21.78</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.71</v>
+        <v>21.74</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.86</v>
+        <v>21.88</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.12</v>
+        <v>21.16</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.09</v>
+        <v>21.17</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.87</v>
+        <v>21.83</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.86</v>
+        <v>21.84</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.15</v>
+        <v>22.09</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-22T08:26:00    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-23T08:27:58    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.29s</t>
+          <t>1.28s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.34s</t>
+          <t>1.33s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.19s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.88s</t>
+          <t>0.85s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.48s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>1.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>4.71</v>
+        <v>3.82</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.08</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.12</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.78</v>
+        <v>21.83</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.74</v>
+        <v>21.79</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.86</v>
+        <v>21.88</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.88</v>
+        <v>21.85</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.16</v>
+        <v>21.13</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.84</v>
+        <v>21.89</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.09</v>
+        <v>22.11</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>1.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>4.71</v>
+        <v>3.82</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.08</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.12</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.78</v>
+        <v>21.83</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.74</v>
+        <v>21.79</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.86</v>
+        <v>21.88</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.88</v>
+        <v>21.85</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.16</v>
+        <v>21.13</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.84</v>
+        <v>21.89</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.09</v>
+        <v>22.11</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +156,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -200,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +264,15 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,10 +288,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -679,7 +693,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-23T08:27:58    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-24T08:19:35    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -723,22 +737,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.63s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -999,7 +1013,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.49s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1049,19 +1063,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.84s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1231,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1267,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1303,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1339,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1375,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1411,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1447,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1483,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1519,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1591,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1627,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1663,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1699,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1735,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1771,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1843,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1879,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1915,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1951,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1987,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2023,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2059,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2095,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2131,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2167,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2203,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2239,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2275,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2311,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2347,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2383,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2419,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2455,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2491,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2527,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2563,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2599,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2635,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2671,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2707,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2779,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2815,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2851,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2923,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.79</v>
+        <v>21.8</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2959,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2995,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.89</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3031,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3067,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3139,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.17</v>
+        <v>21.16</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3175,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.86</v>
+        <v>21.81</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3211,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.86</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3247,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.11</v>
+        <v>22.04</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3283,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3319,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3355,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3391,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3427,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3535,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3571,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3607,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3643,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3679,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3715,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3751,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3787,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3823,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3859,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3895,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3931,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3967,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +4003,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4039,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4075,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4111,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4183,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4219,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4255,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4291,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4327,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4363,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4399,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4435,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4471,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4507,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4543,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4615,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4651,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4687,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4723,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4759,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4795,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4831,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4867,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4939,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4975,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +5011,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5047,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5119,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5155,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5191,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5227,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5263,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5299,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5371,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5407,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5443,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5479,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5515,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5551,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5587,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5623,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5659,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5695,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5875,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5911,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5983,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6091,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6127,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6163,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6199,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6271,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6379,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6415,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6451,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6595,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6631,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6739,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6775,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6811,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6847,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6883,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6955,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6991,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7027,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7063,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7171,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7207,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7351,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7387,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7459,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7567,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7711,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7747,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7783,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7819,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7855,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7891,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7927,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7999,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8071,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8179,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8215,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8287,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8309,7 +8323,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8503,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8575,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8647,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8683,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8791,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8827,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +9007,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9079,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9137,7 +9151,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9187,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9223,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9331,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9367,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9547,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9763,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9835,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9871,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9979,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10051,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10159,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10231,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10303,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10555,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10627,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10735,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10771,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10807,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10843,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11023,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11095,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11167,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11203,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11347,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11383,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11419,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11455,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11491,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11563,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11743,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11815,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11995,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12067,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12103,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12283,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12571,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12679,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12823,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +13003,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13111,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13255,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13291,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13327,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13363,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13399,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13435,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13507,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13543,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13615,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13651,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13723,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13795,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13831,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +14011,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14047,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14083,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14119,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14155,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14191,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14227,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14263,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14443,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14479,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14515,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14551,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14623,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14803,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14875,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14947,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15091,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15343,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15379,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15487,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15559,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15595,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15667,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15775,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15955,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16459,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16495,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16567,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16711,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16747,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16783,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16819,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16855,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16891,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16963,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16999,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17035,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17143,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17179,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17287,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17323,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17359,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17395,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17431,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17467,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17575,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17647,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17683,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17719,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17755,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17791,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17863,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17899,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17935,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17971,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +18007,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18151,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18187,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18331,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18367,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18403,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18439,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18475,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18547,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18583,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18619,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18655,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18691,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18749,45 +18763,54 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
-      <c r="A490" s="17" t="inlineStr">
+      <c r="A490" s="20" t="inlineStr">
         <is>
           <t>TC_PERF_029</t>
         </is>
       </c>
-      <c r="B490" s="17" t="inlineStr">
+      <c r="B490" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C490" s="17" t="inlineStr">
+      <c r="C490" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D490" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E490" s="18" t="inlineStr">
+      <c r="D490" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E490" s="21" t="inlineStr">
         <is>
           <t>Performance smoke test #29</t>
         </is>
       </c>
-      <c r="F490" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G490" s="17" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H490" s="19" t="inlineStr"/>
+      <c r="F490" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G490" s="20" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="H490" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=153.0.8010.52)
+Stacktrace:
+#0 0x5619b19739fa &lt;unknown&gt;
+#1 0x5619b12a95b9 &lt;unknown&gt;
+#2 0x5619b1290fda &lt;unknow</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
@@ -18857,7 +18880,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18916,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18952,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18988,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19024,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19060,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19096,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19132,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19168,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19204,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19197,7 +19220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:H500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19284,7 +19307,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19343,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19379,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19415,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19451,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19487,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19523,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19559,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19595,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19667,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19703,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19739,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19775,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19811,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19847,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19919,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19955,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19991,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20027,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20063,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20099,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20135,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20171,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20207,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20243,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20279,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20315,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20351,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20387,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20423,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20459,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20495,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20531,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20567,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20603,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20639,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20675,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20711,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20747,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20783,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20855,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20891,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20927,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20999,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.79</v>
+        <v>21.8</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21035,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21071,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.89</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21107,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21143,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21215,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.17</v>
+        <v>21.16</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21251,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.86</v>
+        <v>21.81</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21287,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.86</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21323,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.11</v>
+        <v>22.04</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21359,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21395,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21431,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21467,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21503,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21611,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21647,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21683,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21719,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21755,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21791,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21827,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21863,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21899,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21935,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21971,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +22007,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22043,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22079,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22115,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22151,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22187,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22259,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22295,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22331,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22367,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22403,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22439,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22475,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22511,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22547,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22583,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22619,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22691,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22727,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22763,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22799,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22835,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22871,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22907,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22943,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +23015,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23051,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23087,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23123,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23195,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23231,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23267,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23303,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23339,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23375,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23447,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23483,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23519,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23555,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23591,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23627,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23663,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23699,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23735,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23771,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23951,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23987,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24059,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24167,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24203,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24239,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24275,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24311,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24347,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24455,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24491,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24527,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24671,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24707,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24815,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24851,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24887,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24923,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24959,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25031,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25067,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25103,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25139,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25247,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25283,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25427,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25463,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25535,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25643,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25787,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25823,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25859,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25895,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25931,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25967,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +26003,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26075,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26147,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26255,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26291,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26363,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26376,7 +26399,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26579,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26651,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26723,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26759,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26867,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26880,7 +26903,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27083,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27155,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27204,7 +27227,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27263,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27299,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27407,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27443,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27623,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27839,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27911,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27947,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28055,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28127,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28235,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28307,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28379,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28631,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28703,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28811,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28847,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28883,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28919,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29099,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29171,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29243,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29279,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29423,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29459,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29495,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29531,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29567,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29639,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29819,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29891,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30071,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30143,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30179,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30359,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30647,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30755,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30899,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31079,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31187,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31331,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31367,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31403,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31439,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31475,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31511,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31583,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31619,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31691,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31727,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31799,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31871,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31907,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32087,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32123,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32159,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32195,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32231,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32267,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32303,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32339,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32519,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32555,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32591,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32627,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32699,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32879,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32951,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33023,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33167,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33419,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33455,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33563,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33635,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33671,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33743,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33851,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34031,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34535,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34571,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34643,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34787,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34823,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34859,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34895,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34931,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34967,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35039,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35075,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35111,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35219,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35255,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35363,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35399,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35435,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35471,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35507,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35543,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35651,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35723,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35759,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35795,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35831,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35867,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35939,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35975,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +36011,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36047,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36083,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36227,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36263,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36407,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36443,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36479,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36515,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36551,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36623,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36659,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36695,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36731,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36767,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36816,14 +36839,14 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_029</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B490" s="17" t="inlineStr">
@@ -36843,7 +36866,7 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #29</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
@@ -36852,14 +36875,14 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B491" s="17" t="inlineStr">
@@ -36879,7 +36902,7 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
@@ -36888,14 +36911,14 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B492" s="17" t="inlineStr">
@@ -36915,7 +36938,7 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
@@ -36924,14 +36947,14 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B493" s="17" t="inlineStr">
@@ -36951,7 +36974,7 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
@@ -36960,14 +36983,14 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B494" s="17" t="inlineStr">
@@ -36987,7 +37010,7 @@
       </c>
       <c r="E494" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
@@ -36996,14 +37019,14 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B495" s="17" t="inlineStr">
@@ -37023,7 +37046,7 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
@@ -37032,14 +37055,14 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B496" s="17" t="inlineStr">
@@ -37059,7 +37082,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
@@ -37075,7 +37098,7 @@
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B497" s="17" t="inlineStr">
@@ -37095,7 +37118,7 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
@@ -37104,14 +37127,14 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B498" s="17" t="inlineStr">
@@ -37131,7 +37154,7 @@
       </c>
       <c r="E498" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
@@ -37140,14 +37163,14 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_039</t>
         </is>
       </c>
       <c r="B499" s="17" t="inlineStr">
@@ -37167,7 +37190,7 @@
       </c>
       <c r="E499" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #39</t>
         </is>
       </c>
       <c r="F499" s="17" t="inlineStr">
@@ -37183,7 +37206,7 @@
     <row r="500" ht="16" customHeight="1">
       <c r="A500" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_040</t>
         </is>
       </c>
       <c r="B500" s="17" t="inlineStr">
@@ -37203,7 +37226,7 @@
       </c>
       <c r="E500" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #40</t>
         </is>
       </c>
       <c r="F500" s="17" t="inlineStr">
@@ -37216,44 +37239,8 @@
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
-    <row r="501" ht="16" customHeight="1">
-      <c r="A501" s="17" t="inlineStr">
-        <is>
-          <t>TC_PERF_040</t>
-        </is>
-      </c>
-      <c r="B501" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C501" s="17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D501" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E501" s="18" t="inlineStr">
-        <is>
-          <t>Performance smoke test #40</t>
-        </is>
-      </c>
-      <c r="F501" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G501" s="17" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H501" s="19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H501"/>
+  <autoFilter ref="A1:H500"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37264,7 +37251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37319,8 +37306,53 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>TC_PERF_029</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Performance smoke test #29</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=153.0.8010.52)
+Stacktrace:
+#0 0x5619b19739fa &lt;unknown&gt;
+#1 0x5619b12a95b9 &lt;unknown&gt;
+#2 0x5619b1290fda &lt;unknow</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37342,34 +37374,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Pass %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
@@ -37390,7 +37422,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
@@ -37411,7 +37443,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
@@ -37432,7 +37464,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
@@ -37453,7 +37485,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Form Validation</t>
         </is>
@@ -37474,7 +37506,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
@@ -37495,7 +37527,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
@@ -37516,7 +37548,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
@@ -37525,19 +37557,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Responsive Design</t>
         </is>
@@ -37558,7 +37590,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
@@ -37579,7 +37611,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Session Security</t>
         </is>
@@ -37600,7 +37632,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>UI Validation</t>
         </is>
@@ -37641,216 +37673,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n">
+      <c r="B2" s="27" t="n">
         <v>500</v>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>99.8%</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Failed Tests</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Avg Execution Time</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>1.57s</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>1.63s</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>≤ 3.0s</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Test Coverage (Pages)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>19 routes / 14 page objects</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>All routes</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Automation Framework</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Selenium 4.18 + Python 3.11</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Load Testing</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>k6 — 100 VUs × 60s</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>CI/CD Pipeline</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Report Format</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Excel + HTML + JSON</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -156,11 +156,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -205,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,15 +259,6 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -288,10 +274,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-24T08:19:35    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-25T08:43:16    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -737,22 +723,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.63s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -889,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.38s</t>
+          <t>3.36s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -982,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.85s</t>
+          <t>0.89s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1013,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.49s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1063,19 +1049,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.84s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1106,7 +1092,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.3s</t>
+          <t>1.29s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1231,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1267,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1303,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1339,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1375,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1411,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1447,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1483,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1519,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1555,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1591,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1627,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1663,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1699,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1735,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1771,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1807,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1843,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1879,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1915,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1951,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1987,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2023,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2059,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2095,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2131,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2167,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2203,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2239,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2275,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2311,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2383,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2419,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2455,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2491,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2527,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2599,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2635,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2671,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2707,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2743,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2779,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.11</v>
+        <v>10.12</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2815,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2851,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.12</v>
+        <v>21.15</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2887,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.83</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2923,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.8</v>
+        <v>21.69</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2959,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.89</v>
+        <v>21.85</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2995,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3031,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3067,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3103,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.13</v>
+        <v>21.11</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3139,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.16</v>
+        <v>21.1</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3175,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.81</v>
+        <v>21.8</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3211,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.86</v>
+        <v>21.82</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3247,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.04</v>
+        <v>22.01</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3319,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3355,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3391,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3427,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3463,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3499,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3535,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3571,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3607,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3643,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3715,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3751,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3787,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3823,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3859,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3895,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3967,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -4003,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4039,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4075,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4111,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4183,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4219,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4255,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4291,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4327,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4363,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4435,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4471,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4507,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4543,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4579,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4615,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4651,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4687,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4723,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4759,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4795,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4867,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4903,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4975,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -5011,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5047,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5083,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5119,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5155,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5191,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5227,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5263,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5299,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5335,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5371,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5407,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5443,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5479,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5515,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5551,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5623,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5659,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5695,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5731,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5767,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5803,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5839,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5875,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5947,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5983,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6019,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6055,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6091,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6163,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6199,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6235,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6271,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6379,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6415,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6739,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6775,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6811,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6847,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6883,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6955,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6991,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7063,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7135,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7171,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7243,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7279,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7387,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7423,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7459,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7567,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7639,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7711,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7747,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7783,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7819,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7855,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7927,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7999,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8107,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8251,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8287,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8323,7 +8309,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8395,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8467,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8503,7 +8489,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8539,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8575,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8647,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8683,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8755,7 +8741,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8791,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8899,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -9007,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9079,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9115,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9151,7 +9137,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9187,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9223,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9367,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9511,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9547,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9763,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9835,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9871,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9979,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10051,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10159,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10231,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10267,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10303,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10483,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10555,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10591,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10627,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10735,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10771,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10843,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10879,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10915,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -11023,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11095,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11347,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11383,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11455,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11491,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11599,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11707,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11815,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11923,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -12103,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12175,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12247,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12283,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12355,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12391,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12499,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12571,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12607,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12679,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12715,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12751,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12823,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12859,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -13003,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13039,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13075,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13111,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13219,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13255,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13327,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13399,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13471,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13615,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13651,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13723,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13759,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13795,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13831,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13903,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13939,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13975,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14011,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14047,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14083,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14155,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14191,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14263,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14299,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14371,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14407,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14443,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14551,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14731,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14767,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14875,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14911,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14947,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14983,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15019,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15055,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15091,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15307,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15379,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15451,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15559,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15667,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15847,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15919,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15955,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15991,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16171,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16351,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16387,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16495,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16603,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16639,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16747,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16819,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16927,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -17035,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17143,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17179,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17215,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17323,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17359,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17395,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17431,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17467,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17503,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17539,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17575,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17611,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17647,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17719,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17755,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17791,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17863,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17899,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17935,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17971,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18007,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18043,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18079,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18115,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18151,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18187,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18223,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18259,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18295,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18331,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18367,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18403,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18439,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18511,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18547,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18583,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18655,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18691,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18763,54 +18749,45 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
-      <c r="A490" s="20" t="inlineStr">
+      <c r="A490" s="17" t="inlineStr">
         <is>
           <t>TC_PERF_029</t>
         </is>
       </c>
-      <c r="B490" s="20" t="inlineStr">
+      <c r="B490" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C490" s="20" t="inlineStr">
+      <c r="C490" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D490" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E490" s="21" t="inlineStr">
+      <c r="D490" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E490" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #29</t>
         </is>
       </c>
-      <c r="F490" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G490" s="20" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="H490" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=153.0.8010.52)
-Stacktrace:
-#0 0x5619b19739fa &lt;unknown&gt;
-#1 0x5619b12a95b9 &lt;unknown&gt;
-#2 0x5619b1290fda &lt;unknow</t>
-        </is>
-      </c>
+      <c r="F490" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G490" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H490" s="19" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
@@ -18844,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18880,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18916,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18952,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18988,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19024,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19060,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19096,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19132,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19168,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19220,7 +19197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H500"/>
+  <dimension ref="A1:H501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19307,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19343,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19379,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19415,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19451,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19487,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19523,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19559,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19595,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19631,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19667,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19703,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19739,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19775,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19811,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19847,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19883,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19919,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19955,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19991,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20027,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20063,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20099,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20135,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20171,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20207,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20243,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20279,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20315,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20351,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20387,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20459,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20495,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20531,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20567,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20603,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20675,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20711,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20747,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20783,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20819,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20855,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.11</v>
+        <v>10.12</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20891,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20927,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.12</v>
+        <v>21.15</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20963,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.83</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20999,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.8</v>
+        <v>21.69</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21035,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.89</v>
+        <v>21.85</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21071,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.89</v>
+        <v>21.8</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21107,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21143,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21179,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.13</v>
+        <v>21.11</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21215,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.16</v>
+        <v>21.1</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21251,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.81</v>
+        <v>21.8</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21287,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.86</v>
+        <v>21.82</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21323,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.04</v>
+        <v>22.01</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21395,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21431,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21467,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21503,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21539,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21575,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21611,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21647,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21683,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21719,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21791,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21827,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21863,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21899,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21935,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21971,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -22043,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22079,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22115,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22151,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22187,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22259,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22295,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22331,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22367,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22403,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22439,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22511,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22547,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22583,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22619,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22655,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22691,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22727,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22763,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22799,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22835,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22871,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22943,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22979,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -23051,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23087,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23123,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23159,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23195,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23231,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23267,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23303,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23339,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23375,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23411,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23447,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23483,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23519,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23555,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23591,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23627,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23699,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23735,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23771,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23807,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23843,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23879,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23915,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23951,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -24023,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24059,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24095,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24131,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24167,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24239,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24275,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24311,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24347,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24455,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24491,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24815,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24851,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24887,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24923,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24959,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -25031,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25067,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25139,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25211,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25247,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25319,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25355,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25463,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25499,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25535,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25643,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25715,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25787,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25823,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25859,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25895,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25931,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -26003,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26075,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26183,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26327,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26363,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26399,7 +26376,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26471,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26543,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26579,7 +26556,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26615,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26651,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26723,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26759,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26831,7 +26808,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26867,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26975,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -27083,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27155,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27191,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27227,7 +27204,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27263,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27299,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27443,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27587,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27623,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27839,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27911,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27947,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -28055,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28127,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28235,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28307,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28343,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28379,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28559,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28631,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28667,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28703,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28811,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28847,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28919,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28955,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28991,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29099,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29171,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29423,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29459,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29531,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29567,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29675,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29783,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29891,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29999,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30179,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30251,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30323,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30359,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30431,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30467,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30575,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30647,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30683,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30755,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30791,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30827,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30899,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30935,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -31079,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31115,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31151,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31187,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31295,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31331,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31403,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31475,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31547,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31691,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31727,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31799,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31835,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31871,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31907,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31979,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -32015,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32051,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32087,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32123,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32159,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32231,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32267,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32339,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32375,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32447,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32483,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32519,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32627,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32807,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32843,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32951,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32987,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33023,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33059,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33095,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33131,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33167,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33383,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33455,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33527,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33635,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33743,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33923,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33995,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34031,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34067,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34247,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34427,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34463,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34571,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34679,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34715,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34823,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34895,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -35003,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35111,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35219,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35255,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35291,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35399,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35435,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35471,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35507,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35543,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35579,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35615,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35651,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35687,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35723,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35795,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35831,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35867,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35939,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35975,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -36011,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36047,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36083,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36119,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36155,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36191,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36227,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36263,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36299,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36335,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36371,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36407,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36443,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36479,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36515,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36587,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36623,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36659,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36731,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36767,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36839,14 +36816,14 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_029</t>
         </is>
       </c>
       <c r="B490" s="17" t="inlineStr">
@@ -36866,7 +36843,7 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #29</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
@@ -36875,14 +36852,14 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B491" s="17" t="inlineStr">
@@ -36902,7 +36879,7 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
@@ -36911,14 +36888,14 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B492" s="17" t="inlineStr">
@@ -36938,7 +36915,7 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
@@ -36947,14 +36924,14 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B493" s="17" t="inlineStr">
@@ -36974,7 +36951,7 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
@@ -36983,14 +36960,14 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B494" s="17" t="inlineStr">
@@ -37010,7 +36987,7 @@
       </c>
       <c r="E494" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
@@ -37019,14 +36996,14 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B495" s="17" t="inlineStr">
@@ -37046,7 +37023,7 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
@@ -37055,14 +37032,14 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B496" s="17" t="inlineStr">
@@ -37082,7 +37059,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
@@ -37091,14 +37068,14 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B497" s="17" t="inlineStr">
@@ -37118,7 +37095,7 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
@@ -37127,14 +37104,14 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B498" s="17" t="inlineStr">
@@ -37154,7 +37131,7 @@
       </c>
       <c r="E498" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
@@ -37163,14 +37140,14 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B499" s="17" t="inlineStr">
@@ -37190,7 +37167,7 @@
       </c>
       <c r="E499" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F499" s="17" t="inlineStr">
@@ -37199,48 +37176,84 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
     <row r="500" ht="16" customHeight="1">
       <c r="A500" s="17" t="inlineStr">
         <is>
+          <t>TC_PERF_039</t>
+        </is>
+      </c>
+      <c r="B500" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C500" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D500" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E500" s="18" t="inlineStr">
+        <is>
+          <t>Performance smoke test #39</t>
+        </is>
+      </c>
+      <c r="F500" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G500" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H500" s="19" t="inlineStr"/>
+    </row>
+    <row r="501" ht="16" customHeight="1">
+      <c r="A501" s="17" t="inlineStr">
+        <is>
           <t>TC_PERF_040</t>
         </is>
       </c>
-      <c r="B500" s="17" t="inlineStr">
+      <c r="B501" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C500" s="17" t="inlineStr">
+      <c r="C501" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D500" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E500" s="18" t="inlineStr">
+      <c r="D501" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E501" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #40</t>
         </is>
       </c>
-      <c r="F500" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G500" s="17" t="n">
+      <c r="F501" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G501" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="H500" s="19" t="inlineStr"/>
+      <c r="H501" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H500"/>
+  <autoFilter ref="A1:H501"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37251,7 +37264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37306,53 +37319,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>TC_PERF_029</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>Performance smoke test #29</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G2" s="20" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=153.0.8010.52)
-Stacktrace:
-#0 0x5619b19739fa &lt;unknown&gt;
-#1 0x5619b12a95b9 &lt;unknown&gt;
-#2 0x5619b1290fda &lt;unknow</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37374,34 +37342,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Pass %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
@@ -37422,7 +37390,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
@@ -37443,7 +37411,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
@@ -37464,7 +37432,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
@@ -37485,7 +37453,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Form Validation</t>
         </is>
@@ -37506,7 +37474,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
@@ -37527,7 +37495,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
@@ -37548,7 +37516,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
@@ -37557,19 +37525,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Responsive Design</t>
         </is>
@@ -37590,7 +37558,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
@@ -37611,7 +37579,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Session Security</t>
         </is>
@@ -37632,7 +37600,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>UI Validation</t>
         </is>
@@ -37673,216 +37641,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>99.8%</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Failed Tests</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="B4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Avg Execution Time</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>1.63s</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>1.57s</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>≤ 3.0s</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Test Coverage (Pages)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>19 routes / 14 page objects</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>All routes</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Automation Framework</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Selenium 4.18 + Python 3.11</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Load Testing</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>k6 — 100 VUs × 60s</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>CI/CD Pipeline</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Report Format</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Excel + HTML + JSON</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-25T08:43:16    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-26T08:29:17    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.56s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.28s</t>
+          <t>1.26s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.04s</t>
+          <t>1.03s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.31s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.89s</t>
+          <t>0.86s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.45s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.17s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.68</v>
+        <v>0.78</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.12</v>
+        <v>10.08</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.15</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.8</v>
+        <v>21.79</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.69</v>
+        <v>21.74</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.8</v>
+        <v>21.85</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.11</v>
+        <v>21.07</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.1</v>
+        <v>21.13</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.8</v>
+        <v>21.85</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.82</v>
+        <v>21.85</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.01</v>
+        <v>22.02</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.68</v>
+        <v>0.78</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.12</v>
+        <v>10.08</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.15</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.8</v>
+        <v>21.79</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.69</v>
+        <v>21.74</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.8</v>
+        <v>21.85</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.11</v>
+        <v>21.07</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.1</v>
+        <v>21.13</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.8</v>
+        <v>21.85</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.82</v>
+        <v>21.85</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.01</v>
+        <v>22.02</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.56s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-09-26T08:29:17    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-09-27T09:06:55    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.56s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.26s</t>
+          <t>1.27s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.03s</t>
+          <t>1.04s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.36s</t>
+          <t>3.38s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.31s</t>
+          <t>1.33s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.86s</t>
+          <t>0.87s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.45s</t>
+          <t>1.46s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.17s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.29s</t>
+          <t>1.3s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.79</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.74</v>
+        <v>21.81</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.83</v>
+        <v>21.88</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.9</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.07</v>
+        <v>21.13</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.85</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.85</v>
+        <v>21.91</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.02</v>
+        <v>22.1</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.79</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.74</v>
+        <v>21.81</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.83</v>
+        <v>21.88</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.9</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.07</v>
+        <v>21.13</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.85</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.85</v>
+        <v>21.91</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.02</v>
+        <v>22.1</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="G204" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.56s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +156,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -200,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +264,15 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePref